--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1EE0E39-B0EE-44CE-A47C-1C01A23CD473}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9437374-5E5D-47D9-B4C2-503A42099995}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,16 +195,16 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -488,8 +488,9 @@
   <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="23.28515625" customWidth="1"/>
-    <col min="3" max="12" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="5"/>
+    <col min="2" max="2" width="23.28515625" style="5" customWidth="1"/>
+    <col min="3" max="12" width="10.7109375" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
@@ -547,36 +548,36 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5" t="s">
+      <c r="D3" s="4"/>
+      <c r="E3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5" t="s">
+      <c r="F3" s="4"/>
+      <c r="G3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="5"/>
+      <c r="L3" s="4"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="2"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -647,7 +648,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6">
+      <c r="A6" s="5">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -656,23 +657,33 @@
       <c r="C6" s="1">
         <v>45</v>
       </c>
-      <c r="D6" s="2"/>
+      <c r="D6" s="1">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="E6" s="1">
         <v>35.1</v>
       </c>
-      <c r="F6" s="2"/>
+      <c r="F6" s="1">
+        <v>70.2</v>
+      </c>
       <c r="G6" s="1">
         <v>26.7</v>
       </c>
-      <c r="H6" s="2"/>
+      <c r="H6" s="1">
+        <v>44.83</v>
+      </c>
       <c r="I6" s="1">
         <v>12</v>
       </c>
-      <c r="J6" s="2"/>
+      <c r="J6" s="1">
+        <v>22</v>
+      </c>
       <c r="K6" s="1">
         <v>13.5</v>
       </c>
-      <c r="L6" s="2"/>
+      <c r="L6" s="1">
+        <v>19.8</v>
+      </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -684,26 +695,26 @@
       <c r="C7" s="1">
         <v>45</v>
       </c>
-      <c r="D7" s="2"/>
+      <c r="D7" s="1"/>
       <c r="E7" s="1">
         <v>35.1</v>
       </c>
-      <c r="F7" s="2"/>
+      <c r="F7" s="1"/>
       <c r="G7" s="1">
         <v>26.7</v>
       </c>
-      <c r="H7" s="2"/>
+      <c r="H7" s="1"/>
       <c r="I7" s="1">
         <v>12</v>
       </c>
-      <c r="J7" s="2"/>
+      <c r="J7" s="1"/>
       <c r="K7" s="1">
         <v>13.5</v>
       </c>
-      <c r="L7" s="2"/>
+      <c r="L7" s="1"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8">
+      <c r="A8" s="5">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -712,23 +723,23 @@
       <c r="C8" s="1">
         <v>45</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="1"/>
       <c r="E8" s="1">
         <v>35.1</v>
       </c>
-      <c r="F8" s="2"/>
+      <c r="F8" s="1"/>
       <c r="G8" s="1">
         <v>26.7</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="1"/>
       <c r="I8" s="1">
         <v>12</v>
       </c>
-      <c r="J8" s="2"/>
+      <c r="J8" s="1"/>
       <c r="K8" s="1">
         <v>13.5</v>
       </c>
-      <c r="L8" s="2"/>
+      <c r="L8" s="1"/>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -740,26 +751,26 @@
       <c r="C9" s="1">
         <v>45</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="1"/>
       <c r="E9" s="1">
         <v>35.1</v>
       </c>
-      <c r="F9" s="2"/>
+      <c r="F9" s="1"/>
       <c r="G9" s="1">
         <v>26.7</v>
       </c>
-      <c r="H9" s="2"/>
+      <c r="H9" s="1"/>
       <c r="I9" s="1">
         <v>12</v>
       </c>
-      <c r="J9" s="2"/>
+      <c r="J9" s="1"/>
       <c r="K9" s="1">
         <v>13.5</v>
       </c>
-      <c r="L9" s="2"/>
+      <c r="L9" s="1"/>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10">
+      <c r="A10" s="5">
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -768,23 +779,23 @@
       <c r="C10" s="1">
         <v>45</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="1"/>
       <c r="E10" s="1">
         <v>35.1</v>
       </c>
-      <c r="F10" s="2"/>
+      <c r="F10" s="1"/>
       <c r="G10" s="1">
         <v>26.7</v>
       </c>
-      <c r="H10" s="2"/>
+      <c r="H10" s="1"/>
       <c r="I10" s="1">
         <v>12</v>
       </c>
-      <c r="J10" s="2"/>
+      <c r="J10" s="1"/>
       <c r="K10" s="1">
         <v>13.5</v>
       </c>
-      <c r="L10" s="2"/>
+      <c r="L10" s="1"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -796,26 +807,26 @@
       <c r="C11" s="1">
         <v>45</v>
       </c>
-      <c r="D11" s="2"/>
+      <c r="D11" s="1"/>
       <c r="E11" s="1">
         <v>35.1</v>
       </c>
-      <c r="F11" s="2"/>
+      <c r="F11" s="1"/>
       <c r="G11" s="1">
         <v>26.7</v>
       </c>
-      <c r="H11" s="2"/>
+      <c r="H11" s="1"/>
       <c r="I11" s="1">
         <v>12</v>
       </c>
-      <c r="J11" s="2"/>
+      <c r="J11" s="1"/>
       <c r="K11" s="1">
         <v>13.5</v>
       </c>
-      <c r="L11" s="2"/>
+      <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="A12" s="5">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -824,23 +835,23 @@
       <c r="C12" s="1">
         <v>45</v>
       </c>
-      <c r="D12" s="2"/>
+      <c r="D12" s="1"/>
       <c r="E12" s="1">
         <v>35.1</v>
       </c>
-      <c r="F12" s="2"/>
+      <c r="F12" s="1"/>
       <c r="G12" s="1">
         <v>26.7</v>
       </c>
-      <c r="H12" s="2"/>
+      <c r="H12" s="1"/>
       <c r="I12" s="1">
         <v>12</v>
       </c>
-      <c r="J12" s="2"/>
+      <c r="J12" s="1"/>
       <c r="K12" s="1">
         <v>13.5</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="1"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -852,26 +863,26 @@
       <c r="C13" s="1">
         <v>45</v>
       </c>
-      <c r="D13" s="2"/>
+      <c r="D13" s="1"/>
       <c r="E13" s="1">
         <v>35.1</v>
       </c>
-      <c r="F13" s="2"/>
+      <c r="F13" s="1"/>
       <c r="G13" s="1">
         <v>26.7</v>
       </c>
-      <c r="H13" s="2"/>
+      <c r="H13" s="1"/>
       <c r="I13" s="1">
         <v>12</v>
       </c>
-      <c r="J13" s="2"/>
+      <c r="J13" s="1"/>
       <c r="K13" s="1">
         <v>13.5</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14">
+      <c r="A14" s="5">
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -880,23 +891,23 @@
       <c r="C14" s="1">
         <v>45</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="1"/>
       <c r="E14" s="1">
         <v>35.1</v>
       </c>
-      <c r="F14" s="2"/>
+      <c r="F14" s="1"/>
       <c r="G14" s="1">
         <v>26.7</v>
       </c>
-      <c r="H14" s="2"/>
+      <c r="H14" s="1"/>
       <c r="I14" s="1">
         <v>12</v>
       </c>
-      <c r="J14" s="2"/>
+      <c r="J14" s="1"/>
       <c r="K14" s="1">
         <v>13.5</v>
       </c>
-      <c r="L14" s="2"/>
+      <c r="L14" s="1"/>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -908,26 +919,26 @@
       <c r="C15" s="1">
         <v>45</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="1"/>
       <c r="E15" s="1">
         <v>35.1</v>
       </c>
-      <c r="F15" s="2"/>
+      <c r="F15" s="1"/>
       <c r="G15" s="1">
         <v>26.7</v>
       </c>
-      <c r="H15" s="2"/>
+      <c r="H15" s="1"/>
       <c r="I15" s="1">
         <v>12</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="1"/>
       <c r="K15" s="1">
         <v>13.5</v>
       </c>
-      <c r="L15" s="2"/>
+      <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16">
+      <c r="A16" s="5">
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -936,23 +947,23 @@
       <c r="C16" s="1">
         <v>45</v>
       </c>
-      <c r="D16" s="2"/>
+      <c r="D16" s="1"/>
       <c r="E16" s="1">
         <v>35.1</v>
       </c>
-      <c r="F16" s="2"/>
+      <c r="F16" s="1"/>
       <c r="G16" s="1">
         <v>26.7</v>
       </c>
-      <c r="H16" s="2"/>
+      <c r="H16" s="1"/>
       <c r="I16" s="1">
         <v>12</v>
       </c>
-      <c r="J16" s="2"/>
+      <c r="J16" s="1"/>
       <c r="K16" s="1">
         <v>13.5</v>
       </c>
-      <c r="L16" s="2"/>
+      <c r="L16" s="1"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -964,26 +975,26 @@
       <c r="C17" s="1">
         <v>45</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" s="1"/>
       <c r="E17" s="1">
         <v>35.1</v>
       </c>
-      <c r="F17" s="2"/>
+      <c r="F17" s="1"/>
       <c r="G17" s="1">
         <v>26.7</v>
       </c>
-      <c r="H17" s="2"/>
+      <c r="H17" s="1"/>
       <c r="I17" s="1">
         <v>12</v>
       </c>
-      <c r="J17" s="2"/>
+      <c r="J17" s="1"/>
       <c r="K17" s="1">
         <v>13.5</v>
       </c>
-      <c r="L17" s="2"/>
+      <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18">
+      <c r="A18" s="5">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -992,23 +1003,23 @@
       <c r="C18" s="1">
         <v>45</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" s="1"/>
       <c r="E18" s="1">
         <v>35.1</v>
       </c>
-      <c r="F18" s="2"/>
+      <c r="F18" s="1"/>
       <c r="G18" s="1">
         <v>26.7</v>
       </c>
-      <c r="H18" s="2"/>
+      <c r="H18" s="1"/>
       <c r="I18" s="1">
         <v>12</v>
       </c>
-      <c r="J18" s="2"/>
+      <c r="J18" s="1"/>
       <c r="K18" s="1">
         <v>13.5</v>
       </c>
-      <c r="L18" s="2"/>
+      <c r="L18" s="1"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1020,26 +1031,26 @@
       <c r="C19" s="1">
         <v>45</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="1"/>
       <c r="E19" s="1">
         <v>35.1</v>
       </c>
-      <c r="F19" s="2"/>
+      <c r="F19" s="1"/>
       <c r="G19" s="1">
         <v>26.7</v>
       </c>
-      <c r="H19" s="2"/>
+      <c r="H19" s="1"/>
       <c r="I19" s="1">
         <v>12</v>
       </c>
-      <c r="J19" s="2"/>
+      <c r="J19" s="1"/>
       <c r="K19" s="1">
         <v>13.5</v>
       </c>
-      <c r="L19" s="2"/>
+      <c r="L19" s="1"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A20" s="2">
+      <c r="A20" s="1">
         <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
@@ -1048,23 +1059,23 @@
       <c r="C20" s="1">
         <v>45</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="1"/>
       <c r="E20" s="1">
         <v>35.1</v>
       </c>
-      <c r="F20" s="2"/>
+      <c r="F20" s="1"/>
       <c r="G20" s="1">
         <v>26.7</v>
       </c>
-      <c r="H20" s="2"/>
+      <c r="H20" s="1"/>
       <c r="I20" s="1">
         <v>12</v>
       </c>
-      <c r="J20" s="2"/>
+      <c r="J20" s="1"/>
       <c r="K20" s="1">
         <v>13.5</v>
       </c>
-      <c r="L20" s="2"/>
+      <c r="L20" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
@@ -1121,36 +1132,36 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5" t="s">
+      <c r="D25" s="4"/>
+      <c r="E25" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5" t="s">
+      <c r="F25" s="4"/>
+      <c r="G25" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H25" s="4"/>
+      <c r="I25" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="4"/>
+      <c r="K25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="5"/>
+      <c r="L25" s="4"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="2"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1221,30 +1232,42 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28">
+      <c r="A28" s="5">
         <v>2</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="C28" s="1">
+        <v>5</v>
+      </c>
+      <c r="D28" s="1">
+        <v>23.6</v>
+      </c>
       <c r="E28" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F28" s="2"/>
+      <c r="F28" s="1">
+        <v>21.9</v>
+      </c>
       <c r="G28" s="1">
         <v>7.4</v>
       </c>
-      <c r="H28" s="2"/>
+      <c r="H28" s="1">
+        <v>13</v>
+      </c>
       <c r="I28" s="1">
         <v>6</v>
       </c>
-      <c r="J28" s="2"/>
+      <c r="J28" s="1">
+        <v>7.9</v>
+      </c>
       <c r="K28" s="1">
         <v>2.8</v>
       </c>
-      <c r="L28" s="2"/>
+      <c r="L28" s="1">
+        <v>13.5</v>
+      </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -1253,50 +1276,54 @@
       <c r="B29" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="2"/>
-      <c r="D29" s="2"/>
+      <c r="C29" s="1">
+        <v>5</v>
+      </c>
+      <c r="D29" s="1"/>
       <c r="E29" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F29" s="2"/>
+      <c r="F29" s="1"/>
       <c r="G29" s="1">
         <v>7.4</v>
       </c>
-      <c r="H29" s="2"/>
+      <c r="H29" s="1"/>
       <c r="I29" s="1">
         <v>6</v>
       </c>
-      <c r="J29" s="2"/>
+      <c r="J29" s="1"/>
       <c r="K29" s="1">
         <v>2.8</v>
       </c>
-      <c r="L29" s="2"/>
+      <c r="L29" s="1"/>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30">
+      <c r="A30" s="5">
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="C30" s="1">
+        <v>5</v>
+      </c>
+      <c r="D30" s="1"/>
       <c r="E30" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F30" s="2"/>
+      <c r="F30" s="1"/>
       <c r="G30" s="1">
         <v>7.4</v>
       </c>
-      <c r="H30" s="2"/>
+      <c r="H30" s="1"/>
       <c r="I30" s="1">
         <v>6</v>
       </c>
-      <c r="J30" s="2"/>
+      <c r="J30" s="1"/>
       <c r="K30" s="1">
         <v>2.8</v>
       </c>
-      <c r="L30" s="2"/>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -1305,50 +1332,54 @@
       <c r="B31" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
+      <c r="C31" s="1">
+        <v>5</v>
+      </c>
+      <c r="D31" s="1"/>
       <c r="E31" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F31" s="2"/>
+      <c r="F31" s="1"/>
       <c r="G31" s="1">
         <v>7.4</v>
       </c>
-      <c r="H31" s="2"/>
+      <c r="H31" s="1"/>
       <c r="I31" s="1">
         <v>6</v>
       </c>
-      <c r="J31" s="2"/>
+      <c r="J31" s="1"/>
       <c r="K31" s="1">
         <v>2.8</v>
       </c>
-      <c r="L31" s="2"/>
+      <c r="L31" s="1"/>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32">
+      <c r="A32" s="5">
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="C32" s="1">
+        <v>5</v>
+      </c>
+      <c r="D32" s="1"/>
       <c r="E32" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F32" s="2"/>
+      <c r="F32" s="1"/>
       <c r="G32" s="1">
         <v>7.4</v>
       </c>
-      <c r="H32" s="2"/>
+      <c r="H32" s="1"/>
       <c r="I32" s="1">
         <v>6</v>
       </c>
-      <c r="J32" s="2"/>
+      <c r="J32" s="1"/>
       <c r="K32" s="1">
         <v>2.8</v>
       </c>
-      <c r="L32" s="2"/>
+      <c r="L32" s="1"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -1357,50 +1388,54 @@
       <c r="B33" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
+      <c r="C33" s="1">
+        <v>5</v>
+      </c>
+      <c r="D33" s="1"/>
       <c r="E33" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F33" s="2"/>
+      <c r="F33" s="1"/>
       <c r="G33" s="1">
         <v>7.4</v>
       </c>
-      <c r="H33" s="2"/>
+      <c r="H33" s="1"/>
       <c r="I33" s="1">
         <v>6</v>
       </c>
-      <c r="J33" s="2"/>
+      <c r="J33" s="1"/>
       <c r="K33" s="1">
         <v>2.8</v>
       </c>
-      <c r="L33" s="2"/>
+      <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34">
+      <c r="A34" s="5">
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="C34" s="1">
+        <v>5</v>
+      </c>
+      <c r="D34" s="1"/>
       <c r="E34" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F34" s="2"/>
+      <c r="F34" s="1"/>
       <c r="G34" s="1">
         <v>7.4</v>
       </c>
-      <c r="H34" s="2"/>
+      <c r="H34" s="1"/>
       <c r="I34" s="1">
         <v>6</v>
       </c>
-      <c r="J34" s="2"/>
+      <c r="J34" s="1"/>
       <c r="K34" s="1">
         <v>2.8</v>
       </c>
-      <c r="L34" s="2"/>
+      <c r="L34" s="1"/>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -1409,50 +1444,54 @@
       <c r="B35" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C35" s="2"/>
-      <c r="D35" s="2"/>
+      <c r="C35" s="1">
+        <v>5</v>
+      </c>
+      <c r="D35" s="1"/>
       <c r="E35" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F35" s="2"/>
+      <c r="F35" s="1"/>
       <c r="G35" s="1">
         <v>7.4</v>
       </c>
-      <c r="H35" s="2"/>
+      <c r="H35" s="1"/>
       <c r="I35" s="1">
         <v>6</v>
       </c>
-      <c r="J35" s="2"/>
+      <c r="J35" s="1"/>
       <c r="K35" s="1">
         <v>2.8</v>
       </c>
-      <c r="L35" s="2"/>
+      <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36">
+      <c r="A36" s="5">
         <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="C36" s="1">
+        <v>5</v>
+      </c>
+      <c r="D36" s="1"/>
       <c r="E36" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F36" s="2"/>
+      <c r="F36" s="1"/>
       <c r="G36" s="1">
         <v>7.4</v>
       </c>
-      <c r="H36" s="2"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="1">
         <v>6</v>
       </c>
-      <c r="J36" s="2"/>
+      <c r="J36" s="1"/>
       <c r="K36" s="1">
         <v>2.8</v>
       </c>
-      <c r="L36" s="2"/>
+      <c r="L36" s="1"/>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
@@ -1461,50 +1500,54 @@
       <c r="B37" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C37" s="2"/>
-      <c r="D37" s="2"/>
+      <c r="C37" s="1">
+        <v>5</v>
+      </c>
+      <c r="D37" s="1"/>
       <c r="E37" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F37" s="2"/>
+      <c r="F37" s="1"/>
       <c r="G37" s="1">
         <v>7.4</v>
       </c>
-      <c r="H37" s="2"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="1">
         <v>6</v>
       </c>
-      <c r="J37" s="2"/>
+      <c r="J37" s="1"/>
       <c r="K37" s="1">
         <v>2.8</v>
       </c>
-      <c r="L37" s="2"/>
+      <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38">
+      <c r="A38" s="5">
         <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="C38" s="1">
+        <v>5</v>
+      </c>
+      <c r="D38" s="1"/>
       <c r="E38" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F38" s="2"/>
+      <c r="F38" s="1"/>
       <c r="G38" s="1">
         <v>7.4</v>
       </c>
-      <c r="H38" s="2"/>
+      <c r="H38" s="1"/>
       <c r="I38" s="1">
         <v>6</v>
       </c>
-      <c r="J38" s="2"/>
+      <c r="J38" s="1"/>
       <c r="K38" s="1">
         <v>2.8</v>
       </c>
-      <c r="L38" s="2"/>
+      <c r="L38" s="1"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -1513,50 +1556,54 @@
       <c r="B39" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C39" s="2"/>
-      <c r="D39" s="2"/>
+      <c r="C39" s="1">
+        <v>5</v>
+      </c>
+      <c r="D39" s="1"/>
       <c r="E39" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F39" s="2"/>
+      <c r="F39" s="1"/>
       <c r="G39" s="1">
         <v>7.4</v>
       </c>
-      <c r="H39" s="2"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="1">
         <v>6</v>
       </c>
-      <c r="J39" s="2"/>
+      <c r="J39" s="1"/>
       <c r="K39" s="1">
         <v>2.8</v>
       </c>
-      <c r="L39" s="2"/>
+      <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40">
+      <c r="A40" s="5">
         <v>14</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C40" s="2"/>
-      <c r="D40" s="2"/>
+      <c r="C40" s="1">
+        <v>5</v>
+      </c>
+      <c r="D40" s="1"/>
       <c r="E40" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F40" s="2"/>
+      <c r="F40" s="1"/>
       <c r="G40" s="1">
         <v>7.4</v>
       </c>
-      <c r="H40" s="2"/>
+      <c r="H40" s="1"/>
       <c r="I40" s="1">
         <v>6</v>
       </c>
-      <c r="J40" s="2"/>
+      <c r="J40" s="1"/>
       <c r="K40" s="1">
         <v>2.8</v>
       </c>
-      <c r="L40" s="2"/>
+      <c r="L40" s="1"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
@@ -1565,50 +1612,54 @@
       <c r="B41" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C41" s="2"/>
-      <c r="D41" s="2"/>
+      <c r="C41" s="1">
+        <v>5</v>
+      </c>
+      <c r="D41" s="1"/>
       <c r="E41" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F41" s="2"/>
+      <c r="F41" s="1"/>
       <c r="G41" s="1">
         <v>7.4</v>
       </c>
-      <c r="H41" s="2"/>
+      <c r="H41" s="1"/>
       <c r="I41" s="1">
         <v>6</v>
       </c>
-      <c r="J41" s="2"/>
+      <c r="J41" s="1"/>
       <c r="K41" s="1">
         <v>2.8</v>
       </c>
-      <c r="L41" s="2"/>
+      <c r="L41" s="1"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="2">
+      <c r="A42" s="1">
         <v>16</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C42" s="2"/>
-      <c r="D42" s="2"/>
+      <c r="C42" s="1">
+        <v>5</v>
+      </c>
+      <c r="D42" s="1"/>
       <c r="E42" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F42" s="2"/>
+      <c r="F42" s="1"/>
       <c r="G42" s="1">
         <v>7.4</v>
       </c>
-      <c r="H42" s="2"/>
+      <c r="H42" s="1"/>
       <c r="I42" s="1">
         <v>6</v>
       </c>
-      <c r="J42" s="2"/>
+      <c r="J42" s="1"/>
       <c r="K42" s="1">
         <v>2.8</v>
       </c>
-      <c r="L42" s="2"/>
+      <c r="L42" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
@@ -1665,36 +1716,36 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="5"/>
-      <c r="E46" s="5" t="s">
+      <c r="D46" s="4"/>
+      <c r="E46" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="5"/>
-      <c r="G46" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="H46" s="5"/>
-      <c r="I46" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="J46" s="5"/>
-      <c r="K46" s="5" t="s">
+      <c r="F46" s="4"/>
+      <c r="G46" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="H46" s="4"/>
+      <c r="I46" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="J46" s="4"/>
+      <c r="K46" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="L46" s="5"/>
+      <c r="L46" s="4"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="2"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -1765,30 +1816,42 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49">
+      <c r="A49" s="5">
         <v>2</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C49" s="2"/>
-      <c r="D49" s="2"/>
+      <c r="C49" s="1">
+        <v>22</v>
+      </c>
+      <c r="D49" s="1">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="E49" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F49" s="2"/>
+      <c r="F49" s="1">
+        <v>12.8</v>
+      </c>
       <c r="G49" s="1">
         <v>3.7</v>
       </c>
-      <c r="H49" s="2"/>
+      <c r="H49" s="1">
+        <v>11.3</v>
+      </c>
       <c r="I49" s="1">
         <v>3</v>
       </c>
-      <c r="J49" s="2"/>
+      <c r="J49" s="1">
+        <v>6.6</v>
+      </c>
       <c r="K49" s="1">
         <v>2.7</v>
       </c>
-      <c r="L49" s="2"/>
+      <c r="L49" s="1">
+        <v>7.4</v>
+      </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="1">
@@ -1797,50 +1860,54 @@
       <c r="B50" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="C50" s="1">
+        <v>22</v>
+      </c>
+      <c r="D50" s="1"/>
       <c r="E50" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F50" s="2"/>
+      <c r="F50" s="1"/>
       <c r="G50" s="1">
         <v>3.7</v>
       </c>
-      <c r="H50" s="2"/>
+      <c r="H50" s="1"/>
       <c r="I50" s="1">
         <v>3</v>
       </c>
-      <c r="J50" s="2"/>
+      <c r="J50" s="1"/>
       <c r="K50" s="1">
         <v>2.7</v>
       </c>
-      <c r="L50" s="2"/>
+      <c r="L50" s="1"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51">
+      <c r="A51" s="5">
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C51" s="2"/>
-      <c r="D51" s="2"/>
+      <c r="C51" s="1">
+        <v>22</v>
+      </c>
+      <c r="D51" s="1"/>
       <c r="E51" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F51" s="2"/>
+      <c r="F51" s="1"/>
       <c r="G51" s="1">
         <v>3.7</v>
       </c>
-      <c r="H51" s="2"/>
+      <c r="H51" s="1"/>
       <c r="I51" s="1">
         <v>3</v>
       </c>
-      <c r="J51" s="2"/>
+      <c r="J51" s="1"/>
       <c r="K51" s="1">
         <v>2.7</v>
       </c>
-      <c r="L51" s="2"/>
+      <c r="L51" s="1"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
@@ -1849,50 +1916,54 @@
       <c r="B52" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="C52" s="1">
+        <v>22</v>
+      </c>
+      <c r="D52" s="1"/>
       <c r="E52" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F52" s="2"/>
+      <c r="F52" s="1"/>
       <c r="G52" s="1">
         <v>3.7</v>
       </c>
-      <c r="H52" s="2"/>
+      <c r="H52" s="1"/>
       <c r="I52" s="1">
         <v>3</v>
       </c>
-      <c r="J52" s="2"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1">
         <v>2.7</v>
       </c>
-      <c r="L52" s="2"/>
+      <c r="L52" s="1"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53">
+      <c r="A53" s="5">
         <v>6</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C53" s="2"/>
-      <c r="D53" s="2"/>
+      <c r="C53" s="1">
+        <v>22</v>
+      </c>
+      <c r="D53" s="1"/>
       <c r="E53" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F53" s="2"/>
+      <c r="F53" s="1"/>
       <c r="G53" s="1">
         <v>3.7</v>
       </c>
-      <c r="H53" s="2"/>
+      <c r="H53" s="1"/>
       <c r="I53" s="1">
         <v>3</v>
       </c>
-      <c r="J53" s="2"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1">
         <v>2.7</v>
       </c>
-      <c r="L53" s="2"/>
+      <c r="L53" s="1"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -1901,50 +1972,54 @@
       <c r="B54" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="C54" s="1">
+        <v>22</v>
+      </c>
+      <c r="D54" s="1"/>
       <c r="E54" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F54" s="2"/>
+      <c r="F54" s="1"/>
       <c r="G54" s="1">
         <v>3.7</v>
       </c>
-      <c r="H54" s="2"/>
+      <c r="H54" s="1"/>
       <c r="I54" s="1">
         <v>3</v>
       </c>
-      <c r="J54" s="2"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1">
         <v>2.7</v>
       </c>
-      <c r="L54" s="2"/>
+      <c r="L54" s="1"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55">
+      <c r="A55" s="5">
         <v>8</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C55" s="2"/>
-      <c r="D55" s="2"/>
+      <c r="C55" s="1">
+        <v>22</v>
+      </c>
+      <c r="D55" s="1"/>
       <c r="E55" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F55" s="2"/>
+      <c r="F55" s="1"/>
       <c r="G55" s="1">
         <v>3.7</v>
       </c>
-      <c r="H55" s="2"/>
+      <c r="H55" s="1"/>
       <c r="I55" s="1">
         <v>3</v>
       </c>
-      <c r="J55" s="2"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1">
         <v>2.7</v>
       </c>
-      <c r="L55" s="2"/>
+      <c r="L55" s="1"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -1953,50 +2028,54 @@
       <c r="B56" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C56" s="2"/>
-      <c r="D56" s="2"/>
+      <c r="C56" s="1">
+        <v>22</v>
+      </c>
+      <c r="D56" s="1"/>
       <c r="E56" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F56" s="2"/>
+      <c r="F56" s="1"/>
       <c r="G56" s="1">
         <v>3.7</v>
       </c>
-      <c r="H56" s="2"/>
+      <c r="H56" s="1"/>
       <c r="I56" s="1">
         <v>3</v>
       </c>
-      <c r="J56" s="2"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1">
         <v>2.7</v>
       </c>
-      <c r="L56" s="2"/>
+      <c r="L56" s="1"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57">
+      <c r="A57" s="5">
         <v>10</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C57" s="2"/>
-      <c r="D57" s="2"/>
+      <c r="C57" s="1">
+        <v>22</v>
+      </c>
+      <c r="D57" s="1"/>
       <c r="E57" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F57" s="2"/>
+      <c r="F57" s="1"/>
       <c r="G57" s="1">
         <v>3.7</v>
       </c>
-      <c r="H57" s="2"/>
+      <c r="H57" s="1"/>
       <c r="I57" s="1">
         <v>3</v>
       </c>
-      <c r="J57" s="2"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1">
         <v>2.7</v>
       </c>
-      <c r="L57" s="2"/>
+      <c r="L57" s="1"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
@@ -2005,50 +2084,54 @@
       <c r="B58" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C58" s="2"/>
-      <c r="D58" s="2"/>
+      <c r="C58" s="1">
+        <v>22</v>
+      </c>
+      <c r="D58" s="1"/>
       <c r="E58" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F58" s="2"/>
+      <c r="F58" s="1"/>
       <c r="G58" s="1">
         <v>3.7</v>
       </c>
-      <c r="H58" s="2"/>
+      <c r="H58" s="1"/>
       <c r="I58" s="1">
         <v>3</v>
       </c>
-      <c r="J58" s="2"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1">
         <v>2.7</v>
       </c>
-      <c r="L58" s="2"/>
+      <c r="L58" s="1"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59">
+      <c r="A59" s="5">
         <v>12</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C59" s="2"/>
-      <c r="D59" s="2"/>
+      <c r="C59" s="1">
+        <v>22</v>
+      </c>
+      <c r="D59" s="1"/>
       <c r="E59" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F59" s="2"/>
+      <c r="F59" s="1"/>
       <c r="G59" s="1">
         <v>3.7</v>
       </c>
-      <c r="H59" s="2"/>
+      <c r="H59" s="1"/>
       <c r="I59" s="1">
         <v>3</v>
       </c>
-      <c r="J59" s="2"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1">
         <v>2.7</v>
       </c>
-      <c r="L59" s="2"/>
+      <c r="L59" s="1"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1">
@@ -2057,50 +2140,54 @@
       <c r="B60" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C60" s="2"/>
-      <c r="D60" s="2"/>
+      <c r="C60" s="1">
+        <v>22</v>
+      </c>
+      <c r="D60" s="1"/>
       <c r="E60" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F60" s="2"/>
+      <c r="F60" s="1"/>
       <c r="G60" s="1">
         <v>3.7</v>
       </c>
-      <c r="H60" s="2"/>
+      <c r="H60" s="1"/>
       <c r="I60" s="1">
         <v>3</v>
       </c>
-      <c r="J60" s="2"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1">
         <v>2.7</v>
       </c>
-      <c r="L60" s="2"/>
+      <c r="L60" s="1"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61">
+      <c r="A61" s="5">
         <v>14</v>
       </c>
       <c r="B61" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
+      <c r="C61" s="1">
+        <v>22</v>
+      </c>
+      <c r="D61" s="1"/>
       <c r="E61" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F61" s="2"/>
+      <c r="F61" s="1"/>
       <c r="G61" s="1">
         <v>3.7</v>
       </c>
-      <c r="H61" s="2"/>
+      <c r="H61" s="1"/>
       <c r="I61" s="1">
         <v>3</v>
       </c>
-      <c r="J61" s="2"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1">
         <v>2.7</v>
       </c>
-      <c r="L61" s="2"/>
+      <c r="L61" s="1"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1">
@@ -2109,53 +2196,73 @@
       <c r="B62" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C62" s="2"/>
-      <c r="D62" s="2"/>
+      <c r="C62" s="1">
+        <v>22</v>
+      </c>
+      <c r="D62" s="1"/>
       <c r="E62" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F62" s="2"/>
+      <c r="F62" s="1"/>
       <c r="G62" s="1">
         <v>3.7</v>
       </c>
-      <c r="H62" s="2"/>
+      <c r="H62" s="1"/>
       <c r="I62" s="1">
         <v>3</v>
       </c>
-      <c r="J62" s="2"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1">
         <v>2.7</v>
       </c>
-      <c r="L62" s="2"/>
+      <c r="L62" s="1"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="2">
+      <c r="A63" s="1">
         <v>16</v>
       </c>
       <c r="B63" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C63" s="2"/>
-      <c r="D63" s="2"/>
+      <c r="C63" s="1">
+        <v>22</v>
+      </c>
+      <c r="D63" s="1"/>
       <c r="E63" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F63" s="2"/>
+      <c r="F63" s="1"/>
       <c r="G63" s="1">
         <v>3.7</v>
       </c>
-      <c r="H63" s="2"/>
+      <c r="H63" s="1"/>
       <c r="I63" s="1">
         <v>3</v>
       </c>
-      <c r="J63" s="2"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1">
         <v>2.7</v>
       </c>
-      <c r="L63" s="2"/>
+      <c r="L63" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C3:D3"/>
@@ -2164,23 +2271,8 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9437374-5E5D-47D9-B4C2-503A42099995}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885729F3-7E88-4612-BD86-DB0296CD4F4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -195,16 +195,16 @@
   <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -488,9 +488,9 @@
   <dimension ref="A1:L63"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.140625" style="5"/>
-    <col min="2" max="2" width="23.28515625" style="5" customWidth="1"/>
-    <col min="3" max="12" width="10.7109375" style="5" customWidth="1"/>
+    <col min="1" max="1" width="9.140625" style="2"/>
+    <col min="2" max="2" width="23.28515625" style="2" customWidth="1"/>
+    <col min="3" max="12" width="10.7109375" style="2" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
@@ -548,36 +548,36 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4" t="s">
+      <c r="D3" s="5"/>
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
+      <c r="F3" s="5"/>
+      <c r="G3" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4"/>
-      <c r="I3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J3" s="5"/>
+      <c r="K3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L3" s="4"/>
+      <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="2"/>
-      <c r="B4" s="2"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -648,7 +648,7 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="5">
+      <c r="A6" s="2">
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
@@ -695,26 +695,36 @@
       <c r="C7" s="1">
         <v>45</v>
       </c>
-      <c r="D7" s="1"/>
+      <c r="D7" s="1">
+        <v>24.9</v>
+      </c>
       <c r="E7" s="1">
         <v>35.1</v>
       </c>
-      <c r="F7" s="1"/>
+      <c r="F7" s="1">
+        <v>80.099999999999994</v>
+      </c>
       <c r="G7" s="1">
         <v>26.7</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="1">
+        <v>37.9</v>
+      </c>
       <c r="I7" s="1">
         <v>12</v>
       </c>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1">
+        <v>18</v>
+      </c>
       <c r="K7" s="1">
         <v>13.5</v>
       </c>
-      <c r="L7" s="1"/>
+      <c r="L7" s="1">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="5">
+      <c r="A8" s="2">
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
@@ -723,23 +733,33 @@
       <c r="C8" s="1">
         <v>45</v>
       </c>
-      <c r="D8" s="1"/>
+      <c r="D8" s="1">
+        <v>21.7</v>
+      </c>
       <c r="E8" s="1">
         <v>35.1</v>
       </c>
-      <c r="F8" s="1"/>
+      <c r="F8" s="1">
+        <v>80.3</v>
+      </c>
       <c r="G8" s="1">
         <v>26.7</v>
       </c>
-      <c r="H8" s="1"/>
+      <c r="H8" s="1">
+        <v>37.9</v>
+      </c>
       <c r="I8" s="1">
         <v>12</v>
       </c>
-      <c r="J8" s="1"/>
+      <c r="J8" s="1">
+        <v>18.2</v>
+      </c>
       <c r="K8" s="1">
         <v>13.5</v>
       </c>
-      <c r="L8" s="1"/>
+      <c r="L8" s="1">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -751,26 +771,36 @@
       <c r="C9" s="1">
         <v>45</v>
       </c>
-      <c r="D9" s="1"/>
+      <c r="D9" s="1">
+        <v>58.2</v>
+      </c>
       <c r="E9" s="1">
         <v>35.1</v>
       </c>
-      <c r="F9" s="1"/>
+      <c r="F9" s="1">
+        <v>80.3</v>
+      </c>
       <c r="G9" s="1">
         <v>26.7</v>
       </c>
-      <c r="H9" s="1"/>
+      <c r="H9" s="1">
+        <v>37.9</v>
+      </c>
       <c r="I9" s="1">
         <v>12</v>
       </c>
-      <c r="J9" s="1"/>
+      <c r="J9" s="1">
+        <v>18.2</v>
+      </c>
       <c r="K9" s="1">
         <v>13.5</v>
       </c>
-      <c r="L9" s="1"/>
+      <c r="L9" s="1">
+        <v>15.9</v>
+      </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="5">
+      <c r="A10" s="2">
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
@@ -826,7 +856,7 @@
       <c r="L11" s="1"/>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="5">
+      <c r="A12" s="2">
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
@@ -882,7 +912,7 @@
       <c r="L13" s="1"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="5">
+      <c r="A14" s="2">
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
@@ -938,7 +968,7 @@
       <c r="L15" s="1"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="5">
+      <c r="A16" s="2">
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
@@ -994,7 +1024,7 @@
       <c r="L17" s="1"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A18" s="5">
+      <c r="A18" s="2">
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
@@ -1132,36 +1162,36 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="2" t="s">
+      <c r="B25" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D25" s="4"/>
-      <c r="E25" s="4" t="s">
+      <c r="D25" s="5"/>
+      <c r="E25" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="4" t="s">
+      <c r="F25" s="5"/>
+      <c r="G25" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H25" s="4"/>
-      <c r="I25" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J25" s="4"/>
-      <c r="K25" s="4" t="s">
+      <c r="H25" s="5"/>
+      <c r="I25" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J25" s="5"/>
+      <c r="K25" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L25" s="4"/>
+      <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1201,7 +1231,7 @@
         <v>9</v>
       </c>
       <c r="C27" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D27" s="1">
         <v>17.2</v>
@@ -1232,14 +1262,14 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A28" s="5">
+      <c r="A28" s="2">
         <v>2</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>11</v>
       </c>
       <c r="C28" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D28" s="1">
         <v>23.6</v>
@@ -1277,53 +1307,73 @@
         <v>14</v>
       </c>
       <c r="C29" s="1">
-        <v>5</v>
-      </c>
-      <c r="D29" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D29" s="1">
+        <v>19.3</v>
+      </c>
       <c r="E29" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F29" s="1"/>
+      <c r="F29" s="1">
+        <v>21.5</v>
+      </c>
       <c r="G29" s="1">
         <v>7.4</v>
       </c>
-      <c r="H29" s="1"/>
+      <c r="H29" s="1">
+        <v>11.2</v>
+      </c>
       <c r="I29" s="1">
         <v>6</v>
       </c>
-      <c r="J29" s="1"/>
+      <c r="J29" s="1">
+        <v>6.6</v>
+      </c>
       <c r="K29" s="1">
         <v>2.8</v>
       </c>
-      <c r="L29" s="1"/>
+      <c r="L29" s="1">
+        <v>12.3</v>
+      </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A30" s="5">
+      <c r="A30" s="2">
         <v>4</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>15</v>
       </c>
       <c r="C30" s="1">
-        <v>5</v>
-      </c>
-      <c r="D30" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D30" s="1">
+        <v>19.3</v>
+      </c>
       <c r="E30" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F30" s="1"/>
+      <c r="F30" s="1">
+        <v>21.5</v>
+      </c>
       <c r="G30" s="1">
         <v>7.4</v>
       </c>
-      <c r="H30" s="1"/>
+      <c r="H30" s="1">
+        <v>11.2</v>
+      </c>
       <c r="I30" s="1">
         <v>6</v>
       </c>
-      <c r="J30" s="1"/>
+      <c r="J30" s="1">
+        <v>6.7</v>
+      </c>
       <c r="K30" s="1">
         <v>2.8</v>
       </c>
-      <c r="L30" s="1"/>
+      <c r="L30" s="1">
+        <v>12.3</v>
+      </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -1333,35 +1383,45 @@
         <v>16</v>
       </c>
       <c r="C31" s="1">
-        <v>5</v>
-      </c>
-      <c r="D31" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="D31" s="1">
+        <v>29.9</v>
+      </c>
       <c r="E31" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F31" s="1"/>
+      <c r="F31" s="1">
+        <v>21.5</v>
+      </c>
       <c r="G31" s="1">
         <v>7.4</v>
       </c>
-      <c r="H31" s="1"/>
+      <c r="H31" s="1">
+        <v>11.2</v>
+      </c>
       <c r="I31" s="1">
         <v>6</v>
       </c>
-      <c r="J31" s="1"/>
+      <c r="J31" s="1">
+        <v>6.7</v>
+      </c>
       <c r="K31" s="1">
         <v>2.8</v>
       </c>
-      <c r="L31" s="1"/>
+      <c r="L31" s="1">
+        <v>12.3</v>
+      </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A32" s="5">
+      <c r="A32" s="2">
         <v>6</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>17</v>
       </c>
       <c r="C32" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1">
@@ -1389,7 +1449,7 @@
         <v>18</v>
       </c>
       <c r="C33" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1">
@@ -1410,14 +1470,14 @@
       <c r="L33" s="1"/>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A34" s="5">
+      <c r="A34" s="2">
         <v>8</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>12</v>
       </c>
       <c r="C34" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1">
@@ -1445,7 +1505,7 @@
         <v>19</v>
       </c>
       <c r="C35" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1">
@@ -1466,14 +1526,14 @@
       <c r="L35" s="1"/>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A36" s="5">
+      <c r="A36" s="2">
         <v>10</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>20</v>
       </c>
       <c r="C36" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
@@ -1501,7 +1561,7 @@
         <v>21</v>
       </c>
       <c r="C37" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
@@ -1522,14 +1582,14 @@
       <c r="L37" s="1"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="5">
+      <c r="A38" s="2">
         <v>12</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>22</v>
       </c>
       <c r="C38" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
@@ -1557,7 +1617,7 @@
         <v>23</v>
       </c>
       <c r="C39" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1">
@@ -1578,14 +1638,14 @@
       <c r="L39" s="1"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="5">
+      <c r="A40" s="2">
         <v>14</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1">
@@ -1613,7 +1673,7 @@
         <v>13</v>
       </c>
       <c r="C41" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1">
@@ -1641,7 +1701,7 @@
         <v>25</v>
       </c>
       <c r="C42" s="1">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1">
@@ -1716,36 +1776,36 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="2" t="s">
+      <c r="B46" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C46" s="4" t="s">
+      <c r="C46" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="D46" s="4"/>
-      <c r="E46" s="4" t="s">
+      <c r="D46" s="5"/>
+      <c r="E46" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="4" t="s">
+      <c r="F46" s="5"/>
+      <c r="G46" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="H46" s="4"/>
-      <c r="I46" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="J46" s="4"/>
-      <c r="K46" s="4" t="s">
+      <c r="H46" s="5"/>
+      <c r="I46" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="J46" s="5"/>
+      <c r="K46" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="L46" s="4"/>
+      <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="2"/>
-      <c r="B47" s="2"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -1816,7 +1876,7 @@
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="5">
+      <c r="A49" s="2">
         <v>2</v>
       </c>
       <c r="B49" s="1" t="s">
@@ -1863,26 +1923,36 @@
       <c r="C50" s="1">
         <v>22</v>
       </c>
-      <c r="D50" s="1"/>
+      <c r="D50" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="E50" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F50" s="1"/>
+      <c r="F50" s="1">
+        <v>10.8</v>
+      </c>
       <c r="G50" s="1">
         <v>3.7</v>
       </c>
-      <c r="H50" s="1"/>
+      <c r="H50" s="1">
+        <v>10.1</v>
+      </c>
       <c r="I50" s="1">
         <v>3</v>
       </c>
-      <c r="J50" s="1"/>
+      <c r="J50" s="1">
+        <v>5.3</v>
+      </c>
       <c r="K50" s="1">
         <v>2.7</v>
       </c>
-      <c r="L50" s="1"/>
+      <c r="L50" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="5">
+      <c r="A51" s="2">
         <v>4</v>
       </c>
       <c r="B51" s="1" t="s">
@@ -1891,23 +1961,33 @@
       <c r="C51" s="1">
         <v>22</v>
       </c>
-      <c r="D51" s="1"/>
+      <c r="D51" s="1">
+        <v>10.199999999999999</v>
+      </c>
       <c r="E51" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F51" s="1"/>
+      <c r="F51" s="1">
+        <v>10.9</v>
+      </c>
       <c r="G51" s="1">
         <v>3.7</v>
       </c>
-      <c r="H51" s="1"/>
+      <c r="H51" s="1">
+        <v>10.1</v>
+      </c>
       <c r="I51" s="1">
         <v>3</v>
       </c>
-      <c r="J51" s="1"/>
+      <c r="J51" s="1">
+        <v>5.3</v>
+      </c>
       <c r="K51" s="1">
         <v>2.7</v>
       </c>
-      <c r="L51" s="1"/>
+      <c r="L51" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="1">
@@ -1919,26 +1999,36 @@
       <c r="C52" s="1">
         <v>22</v>
       </c>
-      <c r="D52" s="1"/>
+      <c r="D52" s="1">
+        <v>31.6</v>
+      </c>
       <c r="E52" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F52" s="1"/>
+      <c r="F52" s="1">
+        <v>10.9</v>
+      </c>
       <c r="G52" s="1">
         <v>3.7</v>
       </c>
-      <c r="H52" s="1"/>
+      <c r="H52" s="1">
+        <v>10.1</v>
+      </c>
       <c r="I52" s="1">
         <v>3</v>
       </c>
-      <c r="J52" s="1"/>
+      <c r="J52" s="1">
+        <v>5.3</v>
+      </c>
       <c r="K52" s="1">
         <v>2.7</v>
       </c>
-      <c r="L52" s="1"/>
+      <c r="L52" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="5">
+      <c r="A53" s="2">
         <v>6</v>
       </c>
       <c r="B53" s="1" t="s">
@@ -1994,7 +2084,7 @@
       <c r="L54" s="1"/>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="5">
+      <c r="A55" s="2">
         <v>8</v>
       </c>
       <c r="B55" s="1" t="s">
@@ -2050,7 +2140,7 @@
       <c r="L56" s="1"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="5">
+      <c r="A57" s="2">
         <v>10</v>
       </c>
       <c r="B57" s="1" t="s">
@@ -2106,7 +2196,7 @@
       <c r="L58" s="1"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="5">
+      <c r="A59" s="2">
         <v>12</v>
       </c>
       <c r="B59" s="1" t="s">
@@ -2162,7 +2252,7 @@
       <c r="L60" s="1"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A61" s="5">
+      <c r="A61" s="2">
         <v>14</v>
       </c>
       <c r="B61" s="1" t="s">
@@ -2247,6 +2337,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A44:L44"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="B46:B47"/>
@@ -2255,22 +2361,6 @@
     <mergeCell ref="G46:H46"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{885729F3-7E88-4612-BD86-DB0296CD4F4F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5D8579-084E-446A-BF5E-976F90E6C912}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,11 +196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,20 +494,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -548,10 +548,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -576,8 +576,8 @@
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -809,23 +809,33 @@
       <c r="C10" s="1">
         <v>45</v>
       </c>
-      <c r="D10" s="1"/>
+      <c r="D10" s="1">
+        <v>59</v>
+      </c>
       <c r="E10" s="1">
         <v>35.1</v>
       </c>
-      <c r="F10" s="1"/>
+      <c r="F10" s="1">
+        <v>63.7</v>
+      </c>
       <c r="G10" s="1">
         <v>26.7</v>
       </c>
-      <c r="H10" s="1"/>
+      <c r="H10" s="1">
+        <v>43.4</v>
+      </c>
       <c r="I10" s="1">
         <v>12</v>
       </c>
-      <c r="J10" s="1"/>
+      <c r="J10" s="1">
+        <v>12.5</v>
+      </c>
       <c r="K10" s="1">
         <v>13.5</v>
       </c>
-      <c r="L10" s="1"/>
+      <c r="L10" s="1">
+        <v>18</v>
+      </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1108,20 +1118,20 @@
       <c r="L20" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1162,10 +1172,10 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1190,8 +1200,8 @@
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1423,23 +1433,33 @@
       <c r="C32" s="1">
         <v>15</v>
       </c>
-      <c r="D32" s="1"/>
+      <c r="D32" s="1">
+        <v>25.4</v>
+      </c>
       <c r="E32" s="1">
         <v>8.8000000000000007</v>
       </c>
-      <c r="F32" s="1"/>
+      <c r="F32" s="1">
+        <v>20.100000000000001</v>
+      </c>
       <c r="G32" s="1">
         <v>7.4</v>
       </c>
-      <c r="H32" s="1"/>
+      <c r="H32" s="1">
+        <v>8.8000000000000007</v>
+      </c>
       <c r="I32" s="1">
         <v>6</v>
       </c>
-      <c r="J32" s="1"/>
+      <c r="J32" s="1">
+        <v>6.4</v>
+      </c>
       <c r="K32" s="1">
         <v>2.8</v>
       </c>
-      <c r="L32" s="1"/>
+      <c r="L32" s="1">
+        <v>14.1</v>
+      </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A33" s="1">
@@ -1722,20 +1742,20 @@
       <c r="L42" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -1776,10 +1796,10 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -1804,8 +1824,8 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2037,23 +2057,33 @@
       <c r="C53" s="1">
         <v>22</v>
       </c>
-      <c r="D53" s="1"/>
+      <c r="D53" s="1">
+        <v>24.5</v>
+      </c>
       <c r="E53" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F53" s="1"/>
+      <c r="F53" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="G53" s="1">
         <v>3.7</v>
       </c>
-      <c r="H53" s="1"/>
+      <c r="H53" s="1">
+        <v>12.1</v>
+      </c>
       <c r="I53" s="1">
         <v>3</v>
       </c>
-      <c r="J53" s="1"/>
+      <c r="J53" s="1">
+        <v>4.5</v>
+      </c>
       <c r="K53" s="1">
         <v>2.7</v>
       </c>
-      <c r="L53" s="1"/>
+      <c r="L53" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="1">
@@ -2337,6 +2367,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C3:D3"/>
@@ -2345,22 +2391,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E5D8579-084E-446A-BF5E-976F90E6C912}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F915A41-D2D4-4952-97A3-6C470C3C0791}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -629,7 +629,7 @@
         <v>46</v>
       </c>
       <c r="G5" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H5" s="1">
         <v>38.200000000000003</v>
@@ -667,7 +667,7 @@
         <v>70.2</v>
       </c>
       <c r="G6" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H6" s="1">
         <v>44.83</v>
@@ -705,7 +705,7 @@
         <v>80.099999999999994</v>
       </c>
       <c r="G7" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H7" s="1">
         <v>37.9</v>
@@ -743,7 +743,7 @@
         <v>80.3</v>
       </c>
       <c r="G8" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1">
         <v>37.9</v>
@@ -781,7 +781,7 @@
         <v>80.3</v>
       </c>
       <c r="G9" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H9" s="1">
         <v>37.9</v>
@@ -819,7 +819,7 @@
         <v>63.7</v>
       </c>
       <c r="G10" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H10" s="1">
         <v>43.4</v>
@@ -847,23 +847,35 @@
       <c r="C11" s="1">
         <v>45</v>
       </c>
-      <c r="D11" s="1"/>
+      <c r="D11" s="1">
+        <f>29.7+17</f>
+        <v>46.7</v>
+      </c>
       <c r="E11" s="1">
         <v>35.1</v>
       </c>
-      <c r="F11" s="1"/>
+      <c r="F11" s="1">
+        <f>57.9-17</f>
+        <v>40.9</v>
+      </c>
       <c r="G11" s="1">
-        <v>26.7</v>
-      </c>
-      <c r="H11" s="1"/>
+        <v>30</v>
+      </c>
+      <c r="H11" s="1">
+        <v>47.1</v>
+      </c>
       <c r="I11" s="1">
         <v>12</v>
       </c>
-      <c r="J11" s="1"/>
+      <c r="J11" s="1">
+        <v>9.6</v>
+      </c>
       <c r="K11" s="1">
         <v>13.5</v>
       </c>
-      <c r="L11" s="1"/>
+      <c r="L11" s="1">
+        <v>12.3</v>
+      </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -881,7 +893,7 @@
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1">
@@ -909,7 +921,7 @@
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1">
@@ -937,7 +949,7 @@
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1">
@@ -965,7 +977,7 @@
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1">
@@ -993,7 +1005,7 @@
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1">
@@ -1021,7 +1033,7 @@
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1">
@@ -1049,7 +1061,7 @@
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1">
@@ -1077,7 +1089,7 @@
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1">
@@ -1105,7 +1117,7 @@
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1">
-        <v>26.7</v>
+        <v>30</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1">
@@ -1247,7 +1259,7 @@
         <v>17.2</v>
       </c>
       <c r="E27" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F27" s="1">
         <v>21.2</v>
@@ -1259,7 +1271,7 @@
         <v>14.7</v>
       </c>
       <c r="I27" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J27" s="1">
         <v>9.1</v>
@@ -1285,7 +1297,7 @@
         <v>23.6</v>
       </c>
       <c r="E28" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F28" s="1">
         <v>21.9</v>
@@ -1297,7 +1309,7 @@
         <v>13</v>
       </c>
       <c r="I28" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J28" s="1">
         <v>7.9</v>
@@ -1323,7 +1335,7 @@
         <v>19.3</v>
       </c>
       <c r="E29" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F29" s="1">
         <v>21.5</v>
@@ -1335,7 +1347,7 @@
         <v>11.2</v>
       </c>
       <c r="I29" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J29" s="1">
         <v>6.6</v>
@@ -1361,7 +1373,7 @@
         <v>19.3</v>
       </c>
       <c r="E30" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F30" s="1">
         <v>21.5</v>
@@ -1373,7 +1385,7 @@
         <v>11.2</v>
       </c>
       <c r="I30" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J30" s="1">
         <v>6.7</v>
@@ -1399,7 +1411,7 @@
         <v>29.9</v>
       </c>
       <c r="E31" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F31" s="1">
         <v>21.5</v>
@@ -1411,7 +1423,7 @@
         <v>11.2</v>
       </c>
       <c r="I31" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J31" s="1">
         <v>6.7</v>
@@ -1437,7 +1449,7 @@
         <v>25.4</v>
       </c>
       <c r="E32" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F32" s="1">
         <v>20.100000000000001</v>
@@ -1449,7 +1461,7 @@
         <v>8.8000000000000007</v>
       </c>
       <c r="I32" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J32" s="1">
         <v>6.4</v>
@@ -1471,23 +1483,33 @@
       <c r="C33" s="1">
         <v>15</v>
       </c>
-      <c r="D33" s="1"/>
+      <c r="D33" s="1">
+        <v>30.7</v>
+      </c>
       <c r="E33" s="1">
-        <v>8.8000000000000007</v>
-      </c>
-      <c r="F33" s="1"/>
+        <v>15</v>
+      </c>
+      <c r="F33" s="1">
+        <v>19.600000000000001</v>
+      </c>
       <c r="G33" s="1">
         <v>7.4</v>
       </c>
-      <c r="H33" s="1"/>
+      <c r="H33" s="1">
+        <v>6.6</v>
+      </c>
       <c r="I33" s="1">
-        <v>6</v>
-      </c>
-      <c r="J33" s="1"/>
+        <v>8</v>
+      </c>
+      <c r="J33" s="1">
+        <v>15.3</v>
+      </c>
       <c r="K33" s="1">
         <v>2.8</v>
       </c>
-      <c r="L33" s="1"/>
+      <c r="L33" s="1">
+        <v>13</v>
+      </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
@@ -1501,7 +1523,7 @@
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F34" s="1"/>
       <c r="G34" s="1">
@@ -1509,7 +1531,7 @@
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J34" s="1"/>
       <c r="K34" s="1">
@@ -1529,7 +1551,7 @@
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F35" s="1"/>
       <c r="G35" s="1">
@@ -1537,7 +1559,7 @@
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J35" s="1"/>
       <c r="K35" s="1">
@@ -1557,7 +1579,7 @@
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F36" s="1"/>
       <c r="G36" s="1">
@@ -1565,7 +1587,7 @@
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J36" s="1"/>
       <c r="K36" s="1">
@@ -1585,7 +1607,7 @@
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F37" s="1"/>
       <c r="G37" s="1">
@@ -1593,7 +1615,7 @@
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J37" s="1"/>
       <c r="K37" s="1">
@@ -1613,7 +1635,7 @@
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F38" s="1"/>
       <c r="G38" s="1">
@@ -1621,7 +1643,7 @@
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J38" s="1"/>
       <c r="K38" s="1">
@@ -1641,7 +1663,7 @@
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F39" s="1"/>
       <c r="G39" s="1">
@@ -1649,7 +1671,7 @@
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J39" s="1"/>
       <c r="K39" s="1">
@@ -1669,7 +1691,7 @@
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F40" s="1"/>
       <c r="G40" s="1">
@@ -1677,7 +1699,7 @@
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J40" s="1"/>
       <c r="K40" s="1">
@@ -1697,7 +1719,7 @@
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F41" s="1"/>
       <c r="G41" s="1">
@@ -1705,7 +1727,7 @@
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J41" s="1"/>
       <c r="K41" s="1">
@@ -1725,7 +1747,7 @@
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1">
-        <v>8.8000000000000007</v>
+        <v>15</v>
       </c>
       <c r="F42" s="1"/>
       <c r="G42" s="1">
@@ -1733,7 +1755,7 @@
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J42" s="1"/>
       <c r="K42" s="1">
@@ -1883,7 +1905,7 @@
         <v>13.1</v>
       </c>
       <c r="I48" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J48" s="1">
         <v>7.7</v>
@@ -1921,7 +1943,7 @@
         <v>11.3</v>
       </c>
       <c r="I49" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J49" s="1">
         <v>6.6</v>
@@ -1959,7 +1981,7 @@
         <v>10.1</v>
       </c>
       <c r="I50" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J50" s="1">
         <v>5.3</v>
@@ -1997,7 +2019,7 @@
         <v>10.1</v>
       </c>
       <c r="I51" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J51" s="1">
         <v>5.3</v>
@@ -2035,7 +2057,7 @@
         <v>10.1</v>
       </c>
       <c r="I52" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J52" s="1">
         <v>5.3</v>
@@ -2073,7 +2095,7 @@
         <v>12.1</v>
       </c>
       <c r="I53" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J53" s="1">
         <v>4.5</v>
@@ -2095,23 +2117,34 @@
       <c r="C54" s="1">
         <v>22</v>
       </c>
-      <c r="D54" s="1"/>
+      <c r="D54" s="1">
+        <f>11.6+15</f>
+        <v>26.6</v>
+      </c>
       <c r="E54" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F54" s="1"/>
+      <c r="F54" s="1">
+        <v>14.3</v>
+      </c>
       <c r="G54" s="1">
         <v>3.7</v>
       </c>
-      <c r="H54" s="1"/>
+      <c r="H54" s="1">
+        <v>10.8</v>
+      </c>
       <c r="I54" s="1">
-        <v>3</v>
-      </c>
-      <c r="J54" s="1"/>
+        <v>5</v>
+      </c>
+      <c r="J54" s="1">
+        <v>13.4</v>
+      </c>
       <c r="K54" s="1">
         <v>2.7</v>
       </c>
-      <c r="L54" s="1"/>
+      <c r="L54" s="1">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
@@ -2133,7 +2166,7 @@
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J55" s="1"/>
       <c r="K55" s="1">
@@ -2161,7 +2194,7 @@
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J56" s="1"/>
       <c r="K56" s="1">
@@ -2189,7 +2222,7 @@
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J57" s="1"/>
       <c r="K57" s="1">
@@ -2217,7 +2250,7 @@
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J58" s="1"/>
       <c r="K58" s="1">
@@ -2245,7 +2278,7 @@
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J59" s="1"/>
       <c r="K59" s="1">
@@ -2273,7 +2306,7 @@
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J60" s="1"/>
       <c r="K60" s="1">
@@ -2301,7 +2334,7 @@
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J61" s="1"/>
       <c r="K61" s="1">
@@ -2329,7 +2362,7 @@
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J62" s="1"/>
       <c r="K62" s="1">
@@ -2357,7 +2390,7 @@
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J63" s="1"/>
       <c r="K63" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7F915A41-D2D4-4952-97A3-6C470C3C0791}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39266D58-96CB-4EDF-A482-296687F10573}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,11 +196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,20 +494,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -548,10 +548,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -576,8 +576,8 @@
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -887,23 +887,34 @@
       <c r="C12" s="1">
         <v>45</v>
       </c>
-      <c r="D12" s="1"/>
+      <c r="D12" s="1">
+        <f>25.8+12+16</f>
+        <v>53.8</v>
+      </c>
       <c r="E12" s="1">
         <v>35.1</v>
       </c>
-      <c r="F12" s="1"/>
+      <c r="F12" s="1">
+        <v>45.5</v>
+      </c>
       <c r="G12" s="1">
         <v>30</v>
       </c>
-      <c r="H12" s="1"/>
+      <c r="H12" s="1">
+        <v>43.9</v>
+      </c>
       <c r="I12" s="1">
         <v>12</v>
       </c>
-      <c r="J12" s="1"/>
+      <c r="J12" s="1">
+        <v>14.8</v>
+      </c>
       <c r="K12" s="1">
         <v>13.5</v>
       </c>
-      <c r="L12" s="1"/>
+      <c r="L12" s="1">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1130,20 +1141,20 @@
       <c r="L20" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1184,10 +1195,10 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1212,8 +1223,8 @@
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1521,23 +1532,33 @@
       <c r="C34" s="1">
         <v>15</v>
       </c>
-      <c r="D34" s="1"/>
+      <c r="D34" s="1">
+        <v>25.4</v>
+      </c>
       <c r="E34" s="1">
         <v>15</v>
       </c>
-      <c r="F34" s="1"/>
+      <c r="F34" s="1">
+        <v>29</v>
+      </c>
       <c r="G34" s="1">
         <v>7.4</v>
       </c>
-      <c r="H34" s="1"/>
+      <c r="H34" s="1">
+        <v>16.399999999999999</v>
+      </c>
       <c r="I34" s="1">
         <v>8</v>
       </c>
-      <c r="J34" s="1"/>
+      <c r="J34" s="1">
+        <v>14.1</v>
+      </c>
       <c r="K34" s="1">
         <v>2.8</v>
       </c>
-      <c r="L34" s="1"/>
+      <c r="L34" s="1">
+        <v>11.3</v>
+      </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A35" s="1">
@@ -1764,20 +1785,20 @@
       <c r="L42" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -1818,10 +1839,10 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -1846,8 +1867,8 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2156,23 +2177,33 @@
       <c r="C55" s="1">
         <v>22</v>
       </c>
-      <c r="D55" s="1"/>
+      <c r="D55" s="1">
+        <v>20.2</v>
+      </c>
       <c r="E55" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F55" s="1"/>
+      <c r="F55" s="1">
+        <v>12.4</v>
+      </c>
       <c r="G55" s="1">
         <v>3.7</v>
       </c>
-      <c r="H55" s="1"/>
+      <c r="H55" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="I55" s="1">
         <v>5</v>
       </c>
-      <c r="J55" s="1"/>
+      <c r="J55" s="1">
+        <v>12.1</v>
+      </c>
       <c r="K55" s="1">
         <v>2.7</v>
       </c>
-      <c r="L55" s="1"/>
+      <c r="L55" s="1">
+        <v>5.6</v>
+      </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="1">
@@ -2400,6 +2431,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A44:L44"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="B46:B47"/>
@@ -2408,22 +2455,6 @@
     <mergeCell ref="G46:H46"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39266D58-96CB-4EDF-A482-296687F10573}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2BDF2-A6CC-4D4F-A4CA-86E06F426F77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -926,23 +926,34 @@
       <c r="C13" s="1">
         <v>45</v>
       </c>
-      <c r="D13" s="1"/>
+      <c r="D13" s="1">
+        <f>60.2+17</f>
+        <v>77.2</v>
+      </c>
       <c r="E13" s="1">
         <v>35.1</v>
       </c>
-      <c r="F13" s="1"/>
+      <c r="F13" s="1">
+        <v>67.5</v>
+      </c>
       <c r="G13" s="1">
         <v>30</v>
       </c>
-      <c r="H13" s="1"/>
+      <c r="H13" s="1">
+        <v>51.3</v>
+      </c>
       <c r="I13" s="1">
         <v>12</v>
       </c>
-      <c r="J13" s="1"/>
+      <c r="J13" s="1">
+        <v>18.399999999999999</v>
+      </c>
       <c r="K13" s="1">
         <v>13.5</v>
       </c>
-      <c r="L13" s="1"/>
+      <c r="L13" s="1">
+        <v>15.6</v>
+      </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1570,23 +1581,33 @@
       <c r="C35" s="1">
         <v>15</v>
       </c>
-      <c r="D35" s="1"/>
+      <c r="D35" s="1">
+        <v>21.1</v>
+      </c>
       <c r="E35" s="1">
         <v>15</v>
       </c>
-      <c r="F35" s="1"/>
+      <c r="F35" s="1">
+        <v>26</v>
+      </c>
       <c r="G35" s="1">
         <v>7.4</v>
       </c>
-      <c r="H35" s="1"/>
+      <c r="H35" s="1">
+        <v>14.4</v>
+      </c>
       <c r="I35" s="1">
         <v>8</v>
       </c>
-      <c r="J35" s="1"/>
+      <c r="J35" s="1">
+        <v>13.1</v>
+      </c>
       <c r="K35" s="1">
         <v>2.8</v>
       </c>
-      <c r="L35" s="1"/>
+      <c r="L35" s="1">
+        <v>10.6</v>
+      </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
@@ -2215,23 +2236,33 @@
       <c r="C56" s="1">
         <v>22</v>
       </c>
-      <c r="D56" s="1"/>
+      <c r="D56" s="1">
+        <v>21.8</v>
+      </c>
       <c r="E56" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F56" s="1"/>
+      <c r="F56" s="1">
+        <v>9.1</v>
+      </c>
       <c r="G56" s="1">
         <v>3.7</v>
       </c>
-      <c r="H56" s="1"/>
+      <c r="H56" s="1">
+        <v>8.6999999999999993</v>
+      </c>
       <c r="I56" s="1">
         <v>5</v>
       </c>
-      <c r="J56" s="1"/>
+      <c r="J56" s="1">
+        <v>11.1</v>
+      </c>
       <c r="K56" s="1">
         <v>2.7</v>
       </c>
-      <c r="L56" s="1"/>
+      <c r="L56" s="1">
+        <v>5</v>
+      </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="2">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B2BDF2-A6CC-4D4F-A4CA-86E06F426F77}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0EA325-384E-43C3-8AD1-DB04FD29C0F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -965,23 +965,33 @@
       <c r="C14" s="1">
         <v>45</v>
       </c>
-      <c r="D14" s="1"/>
+      <c r="D14" s="1">
+        <v>47</v>
+      </c>
       <c r="E14" s="1">
         <v>35.1</v>
       </c>
-      <c r="F14" s="1"/>
+      <c r="F14" s="1">
+        <v>62</v>
+      </c>
       <c r="G14" s="1">
         <v>30</v>
       </c>
-      <c r="H14" s="1"/>
+      <c r="H14" s="1">
+        <v>45</v>
+      </c>
       <c r="I14" s="1">
         <v>12</v>
       </c>
-      <c r="J14" s="1"/>
+      <c r="J14" s="1">
+        <v>14.4</v>
+      </c>
       <c r="K14" s="1">
         <v>13.5</v>
       </c>
-      <c r="L14" s="1"/>
+      <c r="L14" s="1">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -993,23 +1003,33 @@
       <c r="C15" s="1">
         <v>45</v>
       </c>
-      <c r="D15" s="1"/>
+      <c r="D15" s="1">
+        <v>45.8</v>
+      </c>
       <c r="E15" s="1">
         <v>35.1</v>
       </c>
-      <c r="F15" s="1"/>
+      <c r="F15" s="1">
+        <v>62</v>
+      </c>
       <c r="G15" s="1">
         <v>30</v>
       </c>
-      <c r="H15" s="1"/>
+      <c r="H15" s="1">
+        <v>45</v>
+      </c>
       <c r="I15" s="1">
         <v>12</v>
       </c>
-      <c r="J15" s="1"/>
+      <c r="J15" s="1">
+        <v>14.5</v>
+      </c>
       <c r="K15" s="1">
         <v>13.5</v>
       </c>
-      <c r="L15" s="1"/>
+      <c r="L15" s="1">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1021,23 +1041,33 @@
       <c r="C16" s="1">
         <v>45</v>
       </c>
-      <c r="D16" s="1"/>
+      <c r="D16" s="1">
+        <v>113.8</v>
+      </c>
       <c r="E16" s="1">
         <v>35.1</v>
       </c>
-      <c r="F16" s="1"/>
+      <c r="F16" s="1">
+        <v>62</v>
+      </c>
       <c r="G16" s="1">
         <v>30</v>
       </c>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1">
+        <v>45</v>
+      </c>
       <c r="I16" s="1">
         <v>12</v>
       </c>
-      <c r="J16" s="1"/>
+      <c r="J16" s="1">
+        <v>14.5</v>
+      </c>
       <c r="K16" s="1">
         <v>13.5</v>
       </c>
-      <c r="L16" s="1"/>
+      <c r="L16" s="1">
+        <v>11.7</v>
+      </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1619,23 +1649,33 @@
       <c r="C36" s="1">
         <v>15</v>
       </c>
-      <c r="D36" s="1"/>
+      <c r="D36" s="1">
+        <v>16.8</v>
+      </c>
       <c r="E36" s="1">
         <v>15</v>
       </c>
-      <c r="F36" s="1"/>
+      <c r="F36" s="1">
+        <v>24.7</v>
+      </c>
       <c r="G36" s="1">
         <v>7.4</v>
       </c>
-      <c r="H36" s="1"/>
+      <c r="H36" s="1">
+        <v>16.3</v>
+      </c>
       <c r="I36" s="1">
         <v>8</v>
       </c>
-      <c r="J36" s="1"/>
+      <c r="J36" s="1">
+        <v>10.7</v>
+      </c>
       <c r="K36" s="1">
         <v>2.8</v>
       </c>
-      <c r="L36" s="1"/>
+      <c r="L36" s="1">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A37" s="1">
@@ -1647,23 +1687,33 @@
       <c r="C37" s="1">
         <v>15</v>
       </c>
-      <c r="D37" s="1"/>
+      <c r="D37" s="1">
+        <v>16.8</v>
+      </c>
       <c r="E37" s="1">
         <v>15</v>
       </c>
-      <c r="F37" s="1"/>
+      <c r="F37" s="1">
+        <v>24.7</v>
+      </c>
       <c r="G37" s="1">
         <v>7.4</v>
       </c>
-      <c r="H37" s="1"/>
+      <c r="H37" s="1">
+        <v>16.3</v>
+      </c>
       <c r="I37" s="1">
         <v>8</v>
       </c>
-      <c r="J37" s="1"/>
+      <c r="J37" s="1">
+        <v>10.7</v>
+      </c>
       <c r="K37" s="1">
         <v>2.8</v>
       </c>
-      <c r="L37" s="1"/>
+      <c r="L37" s="1">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
@@ -1675,23 +1725,33 @@
       <c r="C38" s="1">
         <v>15</v>
       </c>
-      <c r="D38" s="1"/>
+      <c r="D38" s="1">
+        <v>30.1</v>
+      </c>
       <c r="E38" s="1">
         <v>15</v>
       </c>
-      <c r="F38" s="1"/>
+      <c r="F38" s="1">
+        <v>24.7</v>
+      </c>
       <c r="G38" s="1">
         <v>7.4</v>
       </c>
-      <c r="H38" s="1"/>
+      <c r="H38" s="1">
+        <v>16.3</v>
+      </c>
       <c r="I38" s="1">
         <v>8</v>
       </c>
-      <c r="J38" s="1"/>
+      <c r="J38" s="1">
+        <v>10.7</v>
+      </c>
       <c r="K38" s="1">
         <v>2.8</v>
       </c>
-      <c r="L38" s="1"/>
+      <c r="L38" s="1">
+        <v>9.6</v>
+      </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" s="1">
@@ -2274,23 +2334,33 @@
       <c r="C57" s="1">
         <v>22</v>
       </c>
-      <c r="D57" s="1"/>
+      <c r="D57" s="1">
+        <v>13.4</v>
+      </c>
       <c r="E57" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F57" s="1"/>
+      <c r="F57" s="1">
+        <v>7.8</v>
+      </c>
       <c r="G57" s="1">
         <v>3.7</v>
       </c>
-      <c r="H57" s="1"/>
+      <c r="H57" s="1">
+        <v>7.3</v>
+      </c>
       <c r="I57" s="1">
         <v>5</v>
       </c>
-      <c r="J57" s="1"/>
+      <c r="J57" s="1">
+        <v>9.4</v>
+      </c>
       <c r="K57" s="1">
         <v>2.7</v>
       </c>
-      <c r="L57" s="1"/>
+      <c r="L57" s="1">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="1">
@@ -2302,23 +2372,33 @@
       <c r="C58" s="1">
         <v>22</v>
       </c>
-      <c r="D58" s="1"/>
+      <c r="D58" s="1">
+        <v>13.4</v>
+      </c>
       <c r="E58" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F58" s="1"/>
+      <c r="F58" s="1">
+        <v>7.8</v>
+      </c>
       <c r="G58" s="1">
         <v>3.7</v>
       </c>
-      <c r="H58" s="1"/>
+      <c r="H58" s="1">
+        <v>7.3</v>
+      </c>
       <c r="I58" s="1">
         <v>5</v>
       </c>
-      <c r="J58" s="1"/>
+      <c r="J58" s="1">
+        <v>9.5</v>
+      </c>
       <c r="K58" s="1">
         <v>2.7</v>
       </c>
-      <c r="L58" s="1"/>
+      <c r="L58" s="1">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
@@ -2330,23 +2410,33 @@
       <c r="C59" s="1">
         <v>22</v>
       </c>
-      <c r="D59" s="1"/>
+      <c r="D59" s="1">
+        <v>30.4</v>
+      </c>
       <c r="E59" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F59" s="1"/>
+      <c r="F59" s="1">
+        <v>7.8</v>
+      </c>
       <c r="G59" s="1">
         <v>3.7</v>
       </c>
-      <c r="H59" s="1"/>
+      <c r="H59" s="1">
+        <v>7.3</v>
+      </c>
       <c r="I59" s="1">
         <v>5</v>
       </c>
-      <c r="J59" s="1"/>
+      <c r="J59" s="1">
+        <v>9.5</v>
+      </c>
       <c r="K59" s="1">
         <v>2.7</v>
       </c>
-      <c r="L59" s="1"/>
+      <c r="L59" s="1">
+        <v>3.5</v>
+      </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC0EA325-384E-43C3-8AD1-DB04FD29C0F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1BC003-6282-44A8-9CF4-AB14C1E127B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,11 +196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,20 +494,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -548,10 +548,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -576,8 +576,8 @@
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1079,23 +1079,34 @@
       <c r="C17" s="1">
         <v>45</v>
       </c>
-      <c r="D17" s="1"/>
+      <c r="D17" s="1">
+        <f>78.6+51</f>
+        <v>129.6</v>
+      </c>
       <c r="E17" s="1">
         <v>35.1</v>
       </c>
-      <c r="F17" s="1"/>
+      <c r="F17" s="1">
+        <v>49.6</v>
+      </c>
       <c r="G17" s="1">
         <v>30</v>
       </c>
-      <c r="H17" s="1"/>
+      <c r="H17" s="1">
+        <v>54.3</v>
+      </c>
       <c r="I17" s="1">
         <v>12</v>
       </c>
-      <c r="J17" s="1"/>
+      <c r="J17" s="1">
+        <v>18.7</v>
+      </c>
       <c r="K17" s="1">
         <v>13.5</v>
       </c>
-      <c r="L17" s="1"/>
+      <c r="L17" s="1">
+        <v>24.8</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
@@ -1182,20 +1193,20 @@
       <c r="L20" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1236,10 +1247,10 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1264,8 +1275,8 @@
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1763,23 +1774,33 @@
       <c r="C39" s="1">
         <v>15</v>
       </c>
-      <c r="D39" s="1"/>
+      <c r="D39" s="1">
+        <v>25.4</v>
+      </c>
       <c r="E39" s="1">
         <v>15</v>
       </c>
-      <c r="F39" s="1"/>
+      <c r="F39" s="1">
+        <v>22.6</v>
+      </c>
       <c r="G39" s="1">
         <v>7.4</v>
       </c>
-      <c r="H39" s="1"/>
+      <c r="H39" s="1">
+        <v>14.6</v>
+      </c>
       <c r="I39" s="1">
         <v>8</v>
       </c>
-      <c r="J39" s="1"/>
+      <c r="J39" s="1">
+        <v>9.5</v>
+      </c>
       <c r="K39" s="1">
         <v>2.8</v>
       </c>
-      <c r="L39" s="1"/>
+      <c r="L39" s="1">
+        <v>9.1</v>
+      </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
@@ -1866,20 +1887,20 @@
       <c r="L42" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -1920,10 +1941,10 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -1948,8 +1969,8 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2448,23 +2469,33 @@
       <c r="C60" s="1">
         <v>22</v>
       </c>
-      <c r="D60" s="1"/>
+      <c r="D60" s="1">
+        <v>24</v>
+      </c>
       <c r="E60" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F60" s="1"/>
+      <c r="F60" s="1">
+        <v>6.2</v>
+      </c>
       <c r="G60" s="1">
         <v>3.7</v>
       </c>
-      <c r="H60" s="1"/>
+      <c r="H60" s="1">
+        <v>4.5</v>
+      </c>
       <c r="I60" s="1">
         <v>5</v>
       </c>
-      <c r="J60" s="1"/>
+      <c r="J60" s="1">
+        <v>8.1999999999999993</v>
+      </c>
       <c r="K60" s="1">
         <v>2.7</v>
       </c>
-      <c r="L60" s="1"/>
+      <c r="L60" s="1">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
@@ -2552,6 +2583,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C3:D3"/>
@@ -2560,22 +2607,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1BC003-6282-44A8-9CF4-AB14C1E127B8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C225FB-7244-4D22-BE54-EA598237F1B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1118,23 +1118,34 @@
       <c r="C18" s="1">
         <v>45</v>
       </c>
-      <c r="D18" s="1"/>
+      <c r="D18" s="1">
+        <f>83.9+17.5</f>
+        <v>101.4</v>
+      </c>
       <c r="E18" s="1">
         <v>35.1</v>
       </c>
-      <c r="F18" s="1"/>
+      <c r="F18" s="1">
+        <v>41.2</v>
+      </c>
       <c r="G18" s="1">
         <v>30</v>
       </c>
-      <c r="H18" s="1"/>
+      <c r="H18" s="1">
+        <v>46.3</v>
+      </c>
       <c r="I18" s="1">
         <v>12</v>
       </c>
-      <c r="J18" s="1"/>
+      <c r="J18" s="1">
+        <v>24.9</v>
+      </c>
       <c r="K18" s="1">
         <v>13.5</v>
       </c>
-      <c r="L18" s="1"/>
+      <c r="L18" s="1">
+        <v>22.3</v>
+      </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1812,23 +1823,33 @@
       <c r="C40" s="1">
         <v>15</v>
       </c>
-      <c r="D40" s="1"/>
+      <c r="D40" s="1">
+        <v>33.1</v>
+      </c>
       <c r="E40" s="1">
         <v>15</v>
       </c>
-      <c r="F40" s="1"/>
+      <c r="F40" s="1">
+        <v>20.3</v>
+      </c>
       <c r="G40" s="1">
         <v>7.4</v>
       </c>
-      <c r="H40" s="1"/>
+      <c r="H40" s="1">
+        <v>12</v>
+      </c>
       <c r="I40" s="1">
         <v>8</v>
       </c>
-      <c r="J40" s="1"/>
+      <c r="J40" s="1">
+        <v>8.4</v>
+      </c>
       <c r="K40" s="1">
         <v>2.8</v>
       </c>
-      <c r="L40" s="1"/>
+      <c r="L40" s="1">
+        <v>8.3000000000000007</v>
+      </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" s="1">
@@ -2507,23 +2528,34 @@
       <c r="C61" s="1">
         <v>22</v>
       </c>
-      <c r="D61" s="1"/>
+      <c r="D61" s="1">
+        <f>32.3+14</f>
+        <v>46.3</v>
+      </c>
       <c r="E61" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F61" s="1"/>
+      <c r="F61" s="1">
+        <v>4.5</v>
+      </c>
       <c r="G61" s="1">
         <v>3.7</v>
       </c>
-      <c r="H61" s="1"/>
+      <c r="H61" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="I61" s="1">
         <v>5</v>
       </c>
-      <c r="J61" s="1"/>
+      <c r="J61" s="1">
+        <v>6.4</v>
+      </c>
       <c r="K61" s="1">
         <v>2.7</v>
       </c>
-      <c r="L61" s="1"/>
+      <c r="L61" s="1">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4C225FB-7244-4D22-BE54-EA598237F1B1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABC134C-033C-4842-9D0F-8F2D96532E4E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,11 +196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,20 +494,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
+      <c r="D1" s="3"/>
+      <c r="E1" s="3"/>
+      <c r="F1" s="3"/>
+      <c r="G1" s="3"/>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3"/>
+      <c r="J1" s="3"/>
+      <c r="K1" s="3"/>
+      <c r="L1" s="3"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -548,10 +548,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -576,8 +576,8 @@
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="3"/>
-      <c r="B4" s="3"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1157,23 +1157,34 @@
       <c r="C19" s="1">
         <v>45</v>
       </c>
-      <c r="D19" s="1"/>
+      <c r="D19" s="1">
+        <f>79+31</f>
+        <v>110</v>
+      </c>
       <c r="E19" s="1">
         <v>35.1</v>
       </c>
-      <c r="F19" s="1"/>
+      <c r="F19" s="1">
+        <v>54.3</v>
+      </c>
       <c r="G19" s="1">
         <v>30</v>
       </c>
-      <c r="H19" s="1"/>
+      <c r="H19" s="1">
+        <v>56</v>
+      </c>
       <c r="I19" s="1">
         <v>12</v>
       </c>
-      <c r="J19" s="1"/>
+      <c r="J19" s="1">
+        <v>22</v>
+      </c>
       <c r="K19" s="1">
         <v>13.5</v>
       </c>
-      <c r="L19" s="1"/>
+      <c r="L19" s="1">
+        <v>18.8</v>
+      </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1204,20 +1215,20 @@
       <c r="L20" s="1"/>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="4" t="s">
+      <c r="A23" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="4"/>
-      <c r="C23" s="4"/>
-      <c r="D23" s="4"/>
-      <c r="E23" s="4"/>
-      <c r="F23" s="4"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="4"/>
-      <c r="I23" s="4"/>
-      <c r="J23" s="4"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="4"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1258,10 +1269,10 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1286,8 +1297,8 @@
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="3"/>
-      <c r="B26" s="3"/>
+      <c r="A26" s="4"/>
+      <c r="B26" s="4"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1861,23 +1872,33 @@
       <c r="C41" s="1">
         <v>15</v>
       </c>
-      <c r="D41" s="1"/>
+      <c r="D41" s="1">
+        <v>29</v>
+      </c>
       <c r="E41" s="1">
         <v>15</v>
       </c>
-      <c r="F41" s="1"/>
+      <c r="F41" s="1">
+        <v>17.399999999999999</v>
+      </c>
       <c r="G41" s="1">
         <v>7.4</v>
       </c>
-      <c r="H41" s="1"/>
+      <c r="H41" s="1">
+        <v>16.600000000000001</v>
+      </c>
       <c r="I41" s="1">
         <v>8</v>
       </c>
-      <c r="J41" s="1"/>
+      <c r="J41" s="1">
+        <v>15.4</v>
+      </c>
       <c r="K41" s="1">
         <v>2.8</v>
       </c>
-      <c r="L41" s="1"/>
+      <c r="L41" s="1">
+        <v>12.2</v>
+      </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" s="1">
@@ -1908,20 +1929,20 @@
       <c r="L42" s="1"/>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="4" t="s">
+      <c r="A44" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="4"/>
-      <c r="C44" s="4"/>
-      <c r="D44" s="4"/>
-      <c r="E44" s="4"/>
-      <c r="F44" s="4"/>
-      <c r="G44" s="4"/>
-      <c r="H44" s="4"/>
-      <c r="I44" s="4"/>
-      <c r="J44" s="4"/>
-      <c r="K44" s="4"/>
-      <c r="L44" s="4"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+      <c r="D44" s="3"/>
+      <c r="E44" s="3"/>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3"/>
+      <c r="H44" s="3"/>
+      <c r="I44" s="3"/>
+      <c r="J44" s="3"/>
+      <c r="K44" s="3"/>
+      <c r="L44" s="3"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -1962,10 +1983,10 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
+      <c r="A46" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="3" t="s">
+      <c r="B46" s="4" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -1990,8 +2011,8 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="3"/>
-      <c r="B47" s="3"/>
+      <c r="A47" s="4"/>
+      <c r="B47" s="4"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2567,23 +2588,34 @@
       <c r="C62" s="1">
         <v>22</v>
       </c>
-      <c r="D62" s="1"/>
+      <c r="D62" s="1">
+        <f>39.6+12</f>
+        <v>51.6</v>
+      </c>
       <c r="E62" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F62" s="1"/>
+      <c r="F62" s="1">
+        <v>10.3</v>
+      </c>
       <c r="G62" s="1">
         <v>3.7</v>
       </c>
-      <c r="H62" s="1"/>
+      <c r="H62" s="1">
+        <v>9.5</v>
+      </c>
       <c r="I62" s="1">
         <v>5</v>
       </c>
-      <c r="J62" s="1"/>
+      <c r="J62" s="1">
+        <v>5.4</v>
+      </c>
       <c r="K62" s="1">
         <v>2.7</v>
       </c>
-      <c r="L62" s="1"/>
+      <c r="L62" s="1">
+        <v>1.1000000000000001</v>
+      </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="1">
@@ -2615,6 +2647,22 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="G3:H3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A44:L44"/>
     <mergeCell ref="A46:A47"/>
     <mergeCell ref="B46:B47"/>
@@ -2623,22 +2671,6 @@
     <mergeCell ref="G46:H46"/>
     <mergeCell ref="I46:J46"/>
     <mergeCell ref="K46:L46"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:L1"/>
-    <mergeCell ref="C3:D3"/>
-    <mergeCell ref="E3:F3"/>
-    <mergeCell ref="G3:H3"/>
-    <mergeCell ref="I3:J3"/>
-    <mergeCell ref="K3:L3"/>
-    <mergeCell ref="B3:B4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EABC134C-033C-4842-9D0F-8F2D96532E4E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714A1C71-FC69-48BB-A2A3-1AC5425B1F36}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -196,11 +196,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -494,20 +494,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -548,10 +548,10 @@
       </c>
     </row>
     <row r="3" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="5" t="s">
@@ -576,8 +576,8 @@
       <c r="L3" s="5"/>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
+      <c r="A4" s="3"/>
+      <c r="B4" s="3"/>
       <c r="C4" s="1" t="s">
         <v>2</v>
       </c>
@@ -1196,39 +1196,50 @@
       <c r="C20" s="1">
         <v>45</v>
       </c>
-      <c r="D20" s="1"/>
+      <c r="D20" s="1">
+        <f>79.6+17</f>
+        <v>96.6</v>
+      </c>
       <c r="E20" s="1">
         <v>35.1</v>
       </c>
-      <c r="F20" s="1"/>
+      <c r="F20" s="1">
+        <v>41.9</v>
+      </c>
       <c r="G20" s="1">
         <v>30</v>
       </c>
-      <c r="H20" s="1"/>
+      <c r="H20" s="1">
+        <v>62.9</v>
+      </c>
       <c r="I20" s="1">
         <v>12</v>
       </c>
-      <c r="J20" s="1"/>
+      <c r="J20" s="1">
+        <v>19.600000000000001</v>
+      </c>
       <c r="K20" s="1">
         <v>13.5</v>
       </c>
-      <c r="L20" s="1"/>
+      <c r="L20" s="1">
+        <v>15.7</v>
+      </c>
     </row>
     <row r="23" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
+      <c r="K23" s="4"/>
+      <c r="L23" s="4"/>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1269,10 +1280,10 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A25" s="4" t="s">
+      <c r="A25" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C25" s="5" t="s">
@@ -1297,8 +1308,8 @@
       <c r="L25" s="5"/>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A26" s="4"/>
-      <c r="B26" s="4"/>
+      <c r="A26" s="3"/>
+      <c r="B26" s="3"/>
       <c r="C26" s="1" t="s">
         <v>2</v>
       </c>
@@ -1910,39 +1921,49 @@
       <c r="C42" s="1">
         <v>15</v>
       </c>
-      <c r="D42" s="1"/>
+      <c r="D42" s="1">
+        <v>24.5</v>
+      </c>
       <c r="E42" s="1">
         <v>15</v>
       </c>
-      <c r="F42" s="1"/>
+      <c r="F42" s="1">
+        <v>15.1</v>
+      </c>
       <c r="G42" s="1">
         <v>7.4</v>
       </c>
-      <c r="H42" s="1"/>
+      <c r="H42" s="1">
+        <v>14.8</v>
+      </c>
       <c r="I42" s="1">
         <v>8</v>
       </c>
-      <c r="J42" s="1"/>
+      <c r="J42" s="1">
+        <v>14</v>
+      </c>
       <c r="K42" s="1">
         <v>2.8</v>
       </c>
-      <c r="L42" s="1"/>
+      <c r="L42" s="1">
+        <v>11.1</v>
+      </c>
     </row>
     <row r="44" spans="1:12" ht="21" x14ac:dyDescent="0.35">
-      <c r="A44" s="3" t="s">
+      <c r="A44" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B44" s="3"/>
-      <c r="C44" s="3"/>
-      <c r="D44" s="3"/>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="G44" s="3"/>
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
-      <c r="L44" s="3"/>
+      <c r="B44" s="4"/>
+      <c r="C44" s="4"/>
+      <c r="D44" s="4"/>
+      <c r="E44" s="4"/>
+      <c r="F44" s="4"/>
+      <c r="G44" s="4"/>
+      <c r="H44" s="4"/>
+      <c r="I44" s="4"/>
+      <c r="J44" s="4"/>
+      <c r="K44" s="4"/>
+      <c r="L44" s="4"/>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -1983,10 +2004,10 @@
       </c>
     </row>
     <row r="46" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A46" s="4" t="s">
+      <c r="A46" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C46" s="5" t="s">
@@ -2011,8 +2032,8 @@
       <c r="L46" s="5"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A47" s="4"/>
-      <c r="B47" s="4"/>
+      <c r="A47" s="3"/>
+      <c r="B47" s="3"/>
       <c r="C47" s="1" t="s">
         <v>2</v>
       </c>
@@ -2627,26 +2648,53 @@
       <c r="C63" s="1">
         <v>22</v>
       </c>
-      <c r="D63" s="1"/>
+      <c r="D63" s="1">
+        <f>32.7+11</f>
+        <v>43.7</v>
+      </c>
       <c r="E63" s="1">
         <v>5.0999999999999996</v>
       </c>
-      <c r="F63" s="1"/>
+      <c r="F63" s="1">
+        <v>8.4</v>
+      </c>
       <c r="G63" s="1">
         <v>3.7</v>
       </c>
-      <c r="H63" s="1"/>
+      <c r="H63" s="1">
+        <v>7.9</v>
+      </c>
       <c r="I63" s="1">
         <v>5</v>
       </c>
-      <c r="J63" s="1"/>
+      <c r="J63" s="1">
+        <v>15</v>
+      </c>
       <c r="K63" s="1">
         <v>2.7</v>
       </c>
-      <c r="L63" s="1"/>
+      <c r="L63" s="1">
+        <v>10</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="A44:L44"/>
+    <mergeCell ref="A46:A47"/>
+    <mergeCell ref="B46:B47"/>
+    <mergeCell ref="C46:D46"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="G46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="K46:L46"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="E25:F25"/>
+    <mergeCell ref="G25:H25"/>
+    <mergeCell ref="I25:J25"/>
+    <mergeCell ref="K25:L25"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="C3:D3"/>
@@ -2655,22 +2703,6 @@
     <mergeCell ref="I3:J3"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B3:B4"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A25:A26"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:D25"/>
-    <mergeCell ref="E25:F25"/>
-    <mergeCell ref="G25:H25"/>
-    <mergeCell ref="I25:J25"/>
-    <mergeCell ref="K25:L25"/>
-    <mergeCell ref="A44:L44"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:D46"/>
-    <mergeCell ref="E46:F46"/>
-    <mergeCell ref="G46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="K46:L46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
